--- a/outputs/evaluation/decision/CF_M01_decision_eval.xlsx
+++ b/outputs/evaluation/decision/CF_M01_decision_eval.xlsx
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -699,7 +699,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -724,7 +724,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -788,7 +788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -846,7 +846,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma.</t>
+          <t>Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma. [...] Augmenta la seguretat del sistema al reduir les portes d’enllaç amb l’exterior, ja que l’única manera d’interactuar amb els microserveis és a través de l’Api Gateway.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Augmenta la seguretat del sistema al reduir les portes d’enllaç amb l’exterior, ja que l’única manera d’interactuar amb els microserveis és a través de l’Api Gateway.</t>
+          <t>És solament l’Api Gateway que s’encarrega de l’autorització i el SSL amb el client.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -906,31 +906,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C_02</t>
+          <t>C_03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dona la capacitat de manegar caigudes parcials del sistema, manegant quins serveis estan en funcionament en tot moment.</t>
+          <t>S’ha decidit la utilització d’AWS i no altres serveis cloud pel seu baix preu i la seva utilització prèvia per part de l’empresa.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M01_M05</t>
+          <t>CF_M01_M07</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8196</v>
+        <v>0.8129</v>
       </c>
     </row>
     <row r="5">
@@ -941,31 +941,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R_23</t>
+          <t>C_01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>És solament l’Api Gateway que s’encarrega de l’autorització i el SSL amb el client.</t>
+          <t>Aquest servei, al ser un servei sense servidor fa que no sigui necessari administrar la infraestructura quan hi ha un augment en el conjunt de dades i usuaris. A més, per poder obtenir les dades d’una manera ràpida, Athena realitza les consultes en paral·lel.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>49</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M01_M04</t>
+          <t>CF_M01_M06</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.6274999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -976,31 +976,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C_03</t>
+          <t>C_01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>L’objectiu d’aquests serveis és formar un data lake on s’emmagatzemi tots els històrics per poder processar-los en el mòdul analític.</t>
+          <t>Perquè sigui la transmissió de dades la més ràpida possible s’han fet ús de dos serveis d’Amazon, que ens permeten realitzar una transmissió en quasi temps real.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M01_M07</t>
+          <t>CF_M01_M06</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8129</v>
+        <v>0.6161</v>
       </c>
     </row>
     <row r="7">
@@ -1011,22 +1011,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C_01</t>
+          <t>C_03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>AU_33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S’ha decidit la utilització d’aquest llenguatge, i no JavaScript, ja que és el llenguatge per defecte per NestJS i perquè gràcies al seu tipatge estàtic permet la detecció d’errors en temps de compilació.</t>
+          <t>L’ús de les particions fa que les consultes d’Amazon Athena no llegeixin totes les dades que hi ha en el bucket. Això s’aconsegueix indicant en la consulta quina partició es vol obtenir i, per tant, Amazon Athena solament buscarà dintre de les carpetes i subcarpetes iguals a aquesta partició.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.6076</v>
+        <v>0.7010999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C_04</t>
+          <t>C_01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>S’ha decidit la utilització d’AWS i no altres serveis cloud pel seu baix preu i la seva utilització prèvia per part de l’empresa.</t>
+          <t>S’ha decidit la utilització d’aquest llenguatge [TypeScript], i no JavaScript, ja que és el llenguatge per defecte per NestJS i perquè gràcies al seu tipatge estàtic permet la detecció d’errors en temps de compilació.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1070,182 +1070,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.7926</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AD_08</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>C_03</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>L’emmagatzament s’ha fet d’aquesta manera, ja que com s’explicarà més endavant, fa que la lectura de dades sigui més eficient.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CF_M01_M07</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0.7194</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>AD_09</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>C_04</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Aquest servei, al ser un servei sense servidor fa que no sigui necessari administrar la infraestructura quan hi ha un augment en el conjunt de dades i usuaris.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CF_M01_M02</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0.7966</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AD_10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>C_01</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>A més, per poder obtenir les dades d’una manera ràpida, Athena realitza les consultes en paral·lel.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CF_M01_M06</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0.6274999999999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AD_11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>C_01</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Perquè sigui la transmissió de dades la més ràpida possible s’han fet ús de dos serveis d’Amazon, que ens permeten realitzar una transmissió en quasi temps real.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CF_M01_M06</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0.6161</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AD_12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>C_03</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>L’ús d’aquestes [particions] fa que les consultes d’Amazon Athena no llegeixin totes les dades que hi ha en el bucket.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CF_M01_M07</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0.7116</v>
+        <v>0.5832000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1312,7 +1137,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CF_M01_AD03</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1325,11 +1150,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AD_08</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6434</v>
+        <v>0.6553</v>
       </c>
     </row>
     <row r="3">
@@ -1345,7 +1170,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CF_M01_AD03</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1358,11 +1183,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AD_09</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.7966</v>
+        <v>0.7010999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -1378,7 +1203,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CF_M01_AD03</t>
+          <t>CF_M01_P03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1391,11 +1216,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_06</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.7165</v>
+        <v>0.7000999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1424,11 +1249,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8215</v>
       </c>
     </row>
     <row r="6">
@@ -1457,11 +1282,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8196</v>
+        <v>0.7896</v>
       </c>
     </row>
     <row r="7">
@@ -1490,7 +1315,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1523,7 +1348,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="G8" t="n">
